--- a/artfynd/A 32697-2021 artfynd.xlsx
+++ b/artfynd/A 32697-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32697-2021 artfynd.xlsx
+++ b/artfynd/A 32697-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10031,6 +10031,228 @@
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127275094</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92627</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Yttre Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>507905</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6607482</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127275093</v>
+      </c>
+      <c r="B78" t="n">
+        <v>92627</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Yttre Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>507893</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6607558</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32697-2021 artfynd.xlsx
+++ b/artfynd/A 32697-2021 artfynd.xlsx
@@ -10036,7 +10036,7 @@
         <v>127275094</v>
       </c>
       <c r="B77" t="n">
-        <v>92627</v>
+        <v>92633</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>127275093</v>
       </c>
       <c r="B78" t="n">
-        <v>92627</v>
+        <v>92633</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 32697-2021 artfynd.xlsx
+++ b/artfynd/A 32697-2021 artfynd.xlsx
@@ -10036,7 +10036,7 @@
         <v>127275094</v>
       </c>
       <c r="B77" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>127275093</v>
       </c>
       <c r="B78" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 32697-2021 artfynd.xlsx
+++ b/artfynd/A 32697-2021 artfynd.xlsx
@@ -10036,7 +10036,7 @@
         <v>127275094</v>
       </c>
       <c r="B77" t="n">
-        <v>92634</v>
+        <v>92638</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>127275093</v>
       </c>
       <c r="B78" t="n">
-        <v>92634</v>
+        <v>92638</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 32697-2021 artfynd.xlsx
+++ b/artfynd/A 32697-2021 artfynd.xlsx
@@ -10036,7 +10036,7 @@
         <v>127275094</v>
       </c>
       <c r="B77" t="n">
-        <v>92638</v>
+        <v>92640</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>127275093</v>
       </c>
       <c r="B78" t="n">
-        <v>92638</v>
+        <v>92640</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 32697-2021 artfynd.xlsx
+++ b/artfynd/A 32697-2021 artfynd.xlsx
@@ -10036,7 +10036,7 @@
         <v>127275094</v>
       </c>
       <c r="B77" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>127275093</v>
       </c>
       <c r="B78" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 32697-2021 artfynd.xlsx
+++ b/artfynd/A 32697-2021 artfynd.xlsx
@@ -10036,7 +10036,7 @@
         <v>127275094</v>
       </c>
       <c r="B77" t="n">
-        <v>92646</v>
+        <v>92649</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>127275093</v>
       </c>
       <c r="B78" t="n">
-        <v>92646</v>
+        <v>92649</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 32697-2021 artfynd.xlsx
+++ b/artfynd/A 32697-2021 artfynd.xlsx
@@ -10036,7 +10036,7 @@
         <v>127275094</v>
       </c>
       <c r="B77" t="n">
-        <v>92649</v>
+        <v>92657</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>127275093</v>
       </c>
       <c r="B78" t="n">
-        <v>92649</v>
+        <v>92657</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 32697-2021 artfynd.xlsx
+++ b/artfynd/A 32697-2021 artfynd.xlsx
@@ -10036,7 +10036,7 @@
         <v>127275094</v>
       </c>
       <c r="B77" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>127275093</v>
       </c>
       <c r="B78" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 32697-2021 artfynd.xlsx
+++ b/artfynd/A 32697-2021 artfynd.xlsx
@@ -10036,7 +10036,7 @@
         <v>127275094</v>
       </c>
       <c r="B77" t="n">
-        <v>92658</v>
+        <v>92627</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>127275093</v>
       </c>
       <c r="B78" t="n">
-        <v>92658</v>
+        <v>92627</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 32697-2021 artfynd.xlsx
+++ b/artfynd/A 32697-2021 artfynd.xlsx
@@ -10036,7 +10036,7 @@
         <v>127275094</v>
       </c>
       <c r="B77" t="n">
-        <v>92627</v>
+        <v>92658</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>127275093</v>
       </c>
       <c r="B78" t="n">
-        <v>92627</v>
+        <v>92658</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 32697-2021 artfynd.xlsx
+++ b/artfynd/A 32697-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96219694</v>
+        <v>127275096</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>720</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Munkhyttan, Vstm</t>
+          <t>Yttre Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507737.2232530275</v>
+        <v>507667</v>
       </c>
       <c r="R2" t="n">
-        <v>6607540.231782812</v>
+        <v>6607499</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0,5-5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,65 +765,61 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96219581</v>
+        <v>103663713</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -850,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507786.4552740214</v>
+        <v>507887</v>
       </c>
       <c r="R3" t="n">
-        <v>6607515.026938878</v>
+        <v>6607547</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,22 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,56 +872,55 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96219709</v>
+        <v>103894692</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>3518</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,22 +930,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507889.776290866</v>
+        <v>507990</v>
       </c>
       <c r="R4" t="n">
-        <v>6607566.868594742</v>
+        <v>6607537</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,27 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>&lt;0,5mhög. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,77 +985,80 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96219665</v>
+        <v>103894694</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>3518</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507645.9500090253</v>
+        <v>507960</v>
       </c>
       <c r="R5" t="n">
-        <v>6607546.118121783</v>
+        <v>6607507</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1128,27 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,80 +1099,83 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96219705</v>
+        <v>103894693</v>
       </c>
       <c r="B6" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507772.6138970219</v>
+        <v>507934</v>
       </c>
       <c r="R6" t="n">
-        <v>6607588.387389706</v>
+        <v>6607532</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1254,27 +1199,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Kring 3dm dbh. Friska. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,77 +1213,78 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96219678</v>
+        <v>127275093</v>
       </c>
       <c r="B7" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>4368</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Munkhyttan, Vstm</t>
+          <t>Yttre Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507816.3476507418</v>
+        <v>507893</v>
       </c>
       <c r="R7" t="n">
-        <v>6607525.211872579</v>
+        <v>6607558</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,27 +1311,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,75 +1327,75 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96219663</v>
+        <v>127275094</v>
       </c>
       <c r="B8" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>4368</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Munkhyttan, Vstm</t>
+          <t>Yttre Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507679.3521374107</v>
+        <v>507905</v>
       </c>
       <c r="R8" t="n">
-        <v>6607575.54198765</v>
+        <v>6607482</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1506,27 +1422,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,31 +1438,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96219672</v>
+        <v>96219655</v>
       </c>
       <c r="B9" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1489,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1602,13 +1503,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507797.5220785853</v>
+        <v>507657</v>
       </c>
       <c r="R9" t="n">
-        <v>6607557.059091083</v>
+        <v>6607542</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1635,24 +1536,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1679,15 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96219708</v>
+        <v>96219656</v>
       </c>
       <c r="B10" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1600,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1728,13 +1614,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507916.0088991307</v>
+        <v>507701</v>
       </c>
       <c r="R10" t="n">
-        <v>6607629.177402395</v>
+        <v>6607613</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1761,24 +1647,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1mhög. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1805,15 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96219718</v>
+        <v>96219657</v>
       </c>
       <c r="B11" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1711,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1854,13 +1725,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508073.2551196839</v>
+        <v>507798</v>
       </c>
       <c r="R11" t="n">
-        <v>6607593.071780563</v>
+        <v>6607553</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1887,24 +1758,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>&lt;0,5mhög. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1931,15 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96219711</v>
+        <v>96219658</v>
       </c>
       <c r="B12" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1822,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1980,13 +1836,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507761.4840360288</v>
+        <v>507655</v>
       </c>
       <c r="R12" t="n">
-        <v>6607576.723385116</v>
+        <v>6607581</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2013,24 +1869,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Frisk, ca 3 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2057,15 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96219697</v>
+        <v>96219659</v>
       </c>
       <c r="B13" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2092,7 +1933,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2106,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507751.9452287574</v>
+        <v>507642</v>
       </c>
       <c r="R13" t="n">
-        <v>6607531.151776706</v>
+        <v>6607533</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2139,24 +1980,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>0,5-5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2183,32 +2014,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96219589</v>
+        <v>96219660</v>
       </c>
       <c r="B14" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2218,12 +2044,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2232,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508076.0997510768</v>
+        <v>507740</v>
       </c>
       <c r="R14" t="n">
-        <v>6607449.335132643</v>
+        <v>6607616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2265,19 +2091,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>&lt;0,5höga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2286,7 +2107,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2305,15 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96219655</v>
+        <v>96219661</v>
       </c>
       <c r="B15" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2340,7 +2155,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2354,13 +2169,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507657.1123658683</v>
+        <v>507701</v>
       </c>
       <c r="R15" t="n">
-        <v>6607542.091838436</v>
+        <v>6607614</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2387,24 +2202,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2431,15 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96219667</v>
+        <v>96219662</v>
       </c>
       <c r="B16" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2466,7 +2266,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2480,13 +2280,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507744.2345413952</v>
+        <v>507663</v>
       </c>
       <c r="R16" t="n">
-        <v>6607582.255125998</v>
+        <v>6607619</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2513,19 +2313,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2557,15 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96219662</v>
+        <v>96219663</v>
       </c>
       <c r="B17" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,13 +2391,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507663.0391659274</v>
+        <v>507680</v>
       </c>
       <c r="R17" t="n">
-        <v>6607619.035445491</v>
+        <v>6607575</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2639,19 +2424,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2683,15 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96219685</v>
+        <v>96219664</v>
       </c>
       <c r="B18" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2718,7 +2488,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2732,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507649.4174518314</v>
+        <v>507642</v>
       </c>
       <c r="R18" t="n">
-        <v>6607586.109481469</v>
+        <v>6607551</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2765,24 +2535,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Kring 5m höga. Kring 0,5-1 dm dbh.. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2809,32 +2569,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96219587</v>
+        <v>96219665</v>
       </c>
       <c r="B19" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>220785</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2844,12 +2599,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2858,13 +2613,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>508029.1151742613</v>
+        <v>507646</v>
       </c>
       <c r="R19" t="n">
-        <v>6607370.780739239</v>
+        <v>6607546</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2891,19 +2646,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2912,7 +2662,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2931,15 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96219687</v>
+        <v>96219666</v>
       </c>
       <c r="B20" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2966,7 +2710,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2980,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507656.4947579241</v>
+        <v>507640</v>
       </c>
       <c r="R20" t="n">
-        <v>6607596.246465694</v>
+        <v>6607531</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3013,24 +2757,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Kring 5 m höga. Ca 0,5-1 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3057,15 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96219719</v>
+        <v>96219667</v>
       </c>
       <c r="B21" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,7 +2821,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3106,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>508071.1987979094</v>
+        <v>507744</v>
       </c>
       <c r="R21" t="n">
-        <v>6607606.226628192</v>
+        <v>6607582</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3139,24 +2868,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>&lt;0,5mhög. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3183,15 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96219703</v>
+        <v>96219668</v>
       </c>
       <c r="B22" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3218,7 +2932,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3232,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>508094.5850833313</v>
+        <v>507744</v>
       </c>
       <c r="R22" t="n">
-        <v>6607576.415551471</v>
+        <v>6607615</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3265,19 +2979,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3309,15 +3013,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96219698</v>
+        <v>96219669</v>
       </c>
       <c r="B23" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,7 +3043,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3358,13 +3057,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507772.268488963</v>
+        <v>507663</v>
       </c>
       <c r="R23" t="n">
-        <v>6607510.442263451</v>
+        <v>6607621</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3391,24 +3090,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>0,5-1dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3435,15 +3124,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96219661</v>
+        <v>96219670</v>
       </c>
       <c r="B24" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3470,7 +3154,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3484,13 +3168,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507701.0751589391</v>
+        <v>507657</v>
       </c>
       <c r="R24" t="n">
-        <v>6607613.546029197</v>
+        <v>6607540</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3517,24 +3201,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>0,5-5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3561,15 +3235,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96219673</v>
+        <v>96219672</v>
       </c>
       <c r="B25" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3610,13 +3279,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507677.8456492132</v>
+        <v>507798</v>
       </c>
       <c r="R25" t="n">
-        <v>6607568.453089974</v>
+        <v>6607557</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3643,19 +3312,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3687,15 +3346,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96219690</v>
+        <v>96219673</v>
       </c>
       <c r="B26" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3722,7 +3376,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3736,13 +3390,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507790.37881866</v>
+        <v>507678</v>
       </c>
       <c r="R26" t="n">
-        <v>6607578.807832841</v>
+        <v>6607569</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3769,24 +3423,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ca 5 m höga, 0,5 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3813,15 +3457,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96219693</v>
+        <v>96219676</v>
       </c>
       <c r="B27" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3848,7 +3487,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3862,10 +3501,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507816.8419937624</v>
+        <v>507840</v>
       </c>
       <c r="R27" t="n">
-        <v>6607531.286528201</v>
+        <v>6607540</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3895,24 +3534,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3939,32 +3568,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96219583</v>
+        <v>96219677</v>
       </c>
       <c r="B28" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222771</v>
+        <v>220785</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3974,12 +3598,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3988,10 +3612,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507814.1402795744</v>
+        <v>508074</v>
       </c>
       <c r="R28" t="n">
-        <v>6607611.249376088</v>
+        <v>6607564</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4021,19 +3645,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4042,7 +3661,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4061,32 +3679,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96219600</v>
+        <v>96219678</v>
       </c>
       <c r="B29" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4096,7 +3709,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4110,10 +3723,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>508110.2845610486</v>
+        <v>507816</v>
       </c>
       <c r="R29" t="n">
-        <v>6607584.547539471</v>
+        <v>6607525</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4143,19 +3756,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4182,15 +3790,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96219689</v>
+        <v>96219679</v>
       </c>
       <c r="B30" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4217,7 +3820,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4231,13 +3834,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>508112.3191274916</v>
+        <v>507669</v>
       </c>
       <c r="R30" t="n">
-        <v>6607581.515172106</v>
+        <v>6607612</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4264,24 +3867,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>Kring 5 m höga. Ca 0,5-1 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4308,32 +3901,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96219593</v>
+        <v>96219680</v>
       </c>
       <c r="B31" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4343,7 +3931,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4357,10 +3945,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507791.9766099557</v>
+        <v>507752</v>
       </c>
       <c r="R31" t="n">
-        <v>6607541.863584839</v>
+        <v>6607534</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4390,19 +3978,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4429,15 +4012,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96219715</v>
+        <v>96219682</v>
       </c>
       <c r="B32" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4464,7 +4042,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4478,10 +4056,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>508045.8318812462</v>
+        <v>507780</v>
       </c>
       <c r="R32" t="n">
-        <v>6607377.902763929</v>
+        <v>6607512</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4511,24 +4089,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>&lt;0,5mhög. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4555,15 +4123,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>96219659</v>
+        <v>96219683</v>
       </c>
       <c r="B33" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4590,7 +4153,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4604,13 +4167,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507641.9208015683</v>
+        <v>507865</v>
       </c>
       <c r="R33" t="n">
-        <v>6607532.950428217</v>
+        <v>6607553</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4637,24 +4200,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>&lt;0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4681,15 +4234,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96219692</v>
+        <v>96219684</v>
       </c>
       <c r="B34" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4716,7 +4264,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4730,13 +4278,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507906.8787598481</v>
+        <v>507846</v>
       </c>
       <c r="R34" t="n">
-        <v>6607631.182621534</v>
+        <v>6607543</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4763,19 +4311,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4807,32 +4345,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96219594</v>
+        <v>96219685</v>
       </c>
       <c r="B35" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4842,7 +4375,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4856,13 +4389,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507836.1039889199</v>
+        <v>507650</v>
       </c>
       <c r="R35" t="n">
-        <v>6607533.351279454</v>
+        <v>6607586</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4889,19 +4422,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Kring 5m höga. Kring 0,5-1 dm dbh.. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4928,15 +4456,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>96219712</v>
+        <v>96219686</v>
       </c>
       <c r="B36" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4963,7 +4486,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4977,13 +4500,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507771.6618041644</v>
+        <v>507636</v>
       </c>
       <c r="R36" t="n">
-        <v>6607558.523787232</v>
+        <v>6607569</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5010,24 +4533,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ca 3 dm dbh.. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>Kring 5 m höga. Kring 0,5-1 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5054,32 +4567,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>96219598</v>
+        <v>96219687</v>
       </c>
       <c r="B37" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5089,7 +4597,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5103,13 +4611,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507818.4178987904</v>
+        <v>507656</v>
       </c>
       <c r="R37" t="n">
-        <v>6607504.970702198</v>
+        <v>6607596</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5136,19 +4644,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Kring 5 m höga. Ca 0,5-1 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5175,15 +4678,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>96219682</v>
+        <v>96219688</v>
       </c>
       <c r="B38" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5224,10 +4722,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507780.3774783477</v>
+        <v>508077</v>
       </c>
       <c r="R38" t="n">
-        <v>6607511.977496385</v>
+        <v>6607567</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5257,24 +4755,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5301,32 +4789,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96219582</v>
+        <v>96219689</v>
       </c>
       <c r="B39" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222771</v>
+        <v>220785</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5336,12 +4819,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5350,10 +4833,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507694.5922620555</v>
+        <v>508113</v>
       </c>
       <c r="R39" t="n">
-        <v>6607560.895468106</v>
+        <v>6607582</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5383,19 +4866,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5404,7 +4882,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5423,15 +4900,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96219670</v>
+        <v>96219690</v>
       </c>
       <c r="B40" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5458,7 +4930,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5472,13 +4944,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507657.1165008708</v>
+        <v>507791</v>
       </c>
       <c r="R40" t="n">
-        <v>6607540.067312564</v>
+        <v>6607579</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5505,24 +4977,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>0,5-5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>Ca 5 m höga, 0,5 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5549,32 +5011,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>96219588</v>
+        <v>96219692</v>
       </c>
       <c r="B41" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222771</v>
+        <v>220785</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5584,12 +5041,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5598,10 +5055,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>508013.329160255</v>
+        <v>507907</v>
       </c>
       <c r="R41" t="n">
-        <v>6607402.634704849</v>
+        <v>6607631</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5631,19 +5088,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5652,7 +5104,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5671,15 +5122,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>96219660</v>
+        <v>96219693</v>
       </c>
       <c r="B42" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5706,7 +5152,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5720,10 +5166,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507740.1085361304</v>
+        <v>507817</v>
       </c>
       <c r="R42" t="n">
-        <v>6607616.15703462</v>
+        <v>6607531</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5753,24 +5199,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>&lt;0,5höga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5797,15 +5233,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>96219676</v>
+        <v>96219694</v>
       </c>
       <c r="B43" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5832,7 +5263,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5846,10 +5277,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507840.1473329263</v>
+        <v>507737</v>
       </c>
       <c r="R43" t="n">
-        <v>6607539.433344953</v>
+        <v>6607540</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5879,24 +5310,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>0,5-5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5923,15 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>96219664</v>
+        <v>96219697</v>
       </c>
       <c r="B44" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5958,7 +5374,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5972,13 +5388,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507641.8836604772</v>
+        <v>507752</v>
       </c>
       <c r="R44" t="n">
-        <v>6607551.171156276</v>
+        <v>6607531</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6005,24 +5421,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>0,5-5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6049,15 +5455,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>96219720</v>
+        <v>96219698</v>
       </c>
       <c r="B45" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6084,7 +5485,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6098,10 +5499,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>508046.8032459757</v>
+        <v>507773</v>
       </c>
       <c r="R45" t="n">
-        <v>6607634.010961391</v>
+        <v>6607511</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6131,24 +5532,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>0,5-1dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6175,32 +5566,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>96219584</v>
+        <v>96219700</v>
       </c>
       <c r="B46" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222771</v>
+        <v>220785</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6210,12 +5596,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6224,10 +5610,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507683.9638937505</v>
+        <v>507823</v>
       </c>
       <c r="R46" t="n">
-        <v>6607551.763300961</v>
+        <v>6607502</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6257,19 +5643,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6278,7 +5659,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6297,15 +5677,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>96219706</v>
+        <v>96219701</v>
       </c>
       <c r="B47" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6332,7 +5707,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6346,10 +5721,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>508110.2582826266</v>
+        <v>507909</v>
       </c>
       <c r="R47" t="n">
-        <v>6607596.694535799</v>
+        <v>6607594</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6379,24 +5754,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6423,15 +5788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>96219700</v>
+        <v>96219702</v>
       </c>
       <c r="B48" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6472,10 +5832,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507823.4932751256</v>
+        <v>507769</v>
       </c>
       <c r="R48" t="n">
-        <v>6607502.45059652</v>
+        <v>6607563</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6505,24 +5865,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>Kring 2 dm dbh. Friska. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6549,15 +5899,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>96219679</v>
+        <v>96219703</v>
       </c>
       <c r="B49" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6584,7 +5929,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6598,13 +5943,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507669.1365549249</v>
+        <v>508094</v>
       </c>
       <c r="R49" t="n">
-        <v>6607612.468308048</v>
+        <v>6607577</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6631,24 +5976,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Kring 5 m höga. Ca 0,5-1 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6675,32 +6010,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>96219596</v>
+        <v>96219704</v>
       </c>
       <c r="B50" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6724,10 +6054,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507732.1511177291</v>
+        <v>508025</v>
       </c>
       <c r="R50" t="n">
-        <v>6607541.23358561</v>
+        <v>6607619</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6757,19 +6087,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>&lt;0,5dmhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6796,15 +6121,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>96219704</v>
+        <v>96219705</v>
       </c>
       <c r="B51" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6845,10 +6165,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>508025.0350883918</v>
+        <v>507772</v>
       </c>
       <c r="R51" t="n">
-        <v>6607618.780629425</v>
+        <v>6607589</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6878,24 +6198,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>&lt;0,5dmhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>Kring 3dm dbh. Friska. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6922,15 +6232,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>96219702</v>
+        <v>96219706</v>
       </c>
       <c r="B52" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6957,7 +6262,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6971,10 +6276,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507768.6114000205</v>
+        <v>508110</v>
       </c>
       <c r="R52" t="n">
-        <v>6607562.566513191</v>
+        <v>6607597</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7004,24 +6309,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Kring 2 dm dbh. Friska. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7048,15 +6343,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>96219666</v>
+        <v>96219708</v>
       </c>
       <c r="B53" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7083,7 +6373,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7097,13 +6387,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507639.8969043524</v>
+        <v>507916</v>
       </c>
       <c r="R53" t="n">
-        <v>6607530.921764066</v>
+        <v>6607629</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7130,24 +6420,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>1mhög. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7174,15 +6454,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>96219717</v>
+        <v>96219709</v>
       </c>
       <c r="B54" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7223,10 +6498,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>508037.6825594997</v>
+        <v>507890</v>
       </c>
       <c r="R54" t="n">
-        <v>6607395.094541627</v>
+        <v>6607567</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7256,19 +6531,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7300,15 +6565,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>96219701</v>
+        <v>96219710</v>
       </c>
       <c r="B55" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7335,7 +6595,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7349,13 +6609,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507909.4916733989</v>
+        <v>507646</v>
       </c>
       <c r="R55" t="n">
-        <v>6607594.24107359</v>
+        <v>6607572</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7382,24 +6642,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>Frisk. Ca 5 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7426,32 +6676,27 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>96219585</v>
+        <v>96219711</v>
       </c>
       <c r="B56" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222771</v>
+        <v>220785</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7461,12 +6706,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7475,10 +6720,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>508051.9118539389</v>
+        <v>507762</v>
       </c>
       <c r="R56" t="n">
-        <v>6607379.940439202</v>
+        <v>6607576</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7508,19 +6753,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Frisk, ca 3 dm dbh. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7529,7 +6769,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7548,32 +6787,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>96219595</v>
+        <v>96219712</v>
       </c>
       <c r="B57" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7583,7 +6817,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7597,10 +6831,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507868.4971138778</v>
+        <v>507772</v>
       </c>
       <c r="R57" t="n">
-        <v>6607559.738042141</v>
+        <v>6607559</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7630,19 +6864,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ca 3 dm dbh.. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7669,32 +6898,27 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>96219597</v>
+        <v>96219715</v>
       </c>
       <c r="B58" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7718,10 +6942,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507813.2908422967</v>
+        <v>508046</v>
       </c>
       <c r="R58" t="n">
-        <v>6607532.291395407</v>
+        <v>6607378</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7751,19 +6975,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>&lt;0,5mhög. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7790,15 +7009,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>96219680</v>
+        <v>96219716</v>
       </c>
       <c r="B59" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7825,7 +7039,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7839,10 +7053,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507751.9389494453</v>
+        <v>508041</v>
       </c>
       <c r="R59" t="n">
-        <v>6607534.188572356</v>
+        <v>6607374</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7872,24 +7086,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhög. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7916,15 +7120,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>96219677</v>
+        <v>96219717</v>
       </c>
       <c r="B60" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7951,7 +7150,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7965,10 +7164,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>508073.8242477943</v>
+        <v>508037</v>
       </c>
       <c r="R60" t="n">
-        <v>6607564.223664522</v>
+        <v>6607395</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7998,24 +7197,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhög. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8042,15 +7231,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>96219656</v>
+        <v>96219718</v>
       </c>
       <c r="B61" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8077,7 +7261,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8091,13 +7275,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507701.0772383243</v>
+        <v>508073</v>
       </c>
       <c r="R61" t="n">
-        <v>6607612.533785617</v>
+        <v>6607593</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8124,24 +7308,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhög. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8168,15 +7342,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>96219683</v>
+        <v>96219719</v>
       </c>
       <c r="B62" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8203,7 +7372,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8217,10 +7386,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507864.9629643446</v>
+        <v>508071</v>
       </c>
       <c r="R62" t="n">
-        <v>6607552.644782584</v>
+        <v>6607606</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8250,24 +7419,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhög. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8294,15 +7453,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>96219668</v>
+        <v>96219720</v>
       </c>
       <c r="B63" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8329,7 +7483,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8343,10 +7497,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507744.1665830315</v>
+        <v>508047</v>
       </c>
       <c r="R63" t="n">
-        <v>6607615.153168052</v>
+        <v>6607634</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8376,24 +7530,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8423,12 +7567,7 @@
         <v>96219721</v>
       </c>
       <c r="B64" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8469,10 +7608,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>508111.2613262395</v>
+        <v>508111</v>
       </c>
       <c r="R64" t="n">
-        <v>6607601.757966475</v>
+        <v>6607601</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8502,19 +7641,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -8546,15 +7675,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>96219658</v>
+        <v>96219722</v>
       </c>
       <c r="B65" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8581,7 +7705,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8595,13 +7719,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>507654.4977712372</v>
+        <v>508075</v>
       </c>
       <c r="R65" t="n">
-        <v>6607581.058572382</v>
+        <v>6607422</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8628,24 +7752,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>&lt;0,5mhög. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8672,15 +7786,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>96219688</v>
+        <v>96219723</v>
       </c>
       <c r="B66" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8705,29 +7814,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>508076.3548940892</v>
+        <v>507642</v>
       </c>
       <c r="R66" t="n">
-        <v>6607566.253637869</v>
+        <v>6607624</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8754,24 +7854,14 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>Område med flera friska mogna askträd på gränsen till eller utanför avverkningsanmälan. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8798,15 +7888,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>96219601</v>
+        <v>96219593</v>
       </c>
       <c r="B67" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8831,17 +7916,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>507682.9405522209</v>
+        <v>507792</v>
       </c>
       <c r="R67" t="n">
-        <v>6607556.316390313</v>
+        <v>6607542</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8871,19 +7965,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8910,32 +7994,27 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>96219657</v>
+        <v>96219594</v>
       </c>
       <c r="B68" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8945,7 +8024,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8959,13 +8038,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>507798.0375032828</v>
+        <v>507836</v>
       </c>
       <c r="R68" t="n">
-        <v>6607553.01110881</v>
+        <v>6607534</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8992,24 +8071,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>&lt;0,5mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9036,32 +8100,27 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>96219684</v>
+        <v>96219595</v>
       </c>
       <c r="B69" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9071,7 +8130,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9085,13 +8144,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>507845.7180312217</v>
+        <v>507869</v>
       </c>
       <c r="R69" t="n">
-        <v>6607542.48180127</v>
+        <v>6607560</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9118,24 +8177,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>0,5-2mhöga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9162,32 +8206,27 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>96219722</v>
+        <v>96219596</v>
       </c>
       <c r="B70" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9197,7 +8236,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9211,10 +8250,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>508075.1434960451</v>
+        <v>507732</v>
       </c>
       <c r="R70" t="n">
-        <v>6607422.507228591</v>
+        <v>6607541</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9244,24 +8283,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>&lt;0,5mhög. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9288,32 +8312,27 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>96219716</v>
+        <v>96219597</v>
       </c>
       <c r="B71" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9337,10 +8356,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>508040.7702981093</v>
+        <v>507813</v>
       </c>
       <c r="R71" t="n">
-        <v>6607373.842656624</v>
+        <v>6607532</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9370,24 +8389,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>&lt;0,5mhög. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9414,37 +8418,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>103663713</v>
+        <v>96219598</v>
       </c>
       <c r="B72" t="n">
-        <v>91607</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>788</v>
+        <v>222412</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -9454,7 +8453,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9463,13 +8462,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>507887</v>
+        <v>507818</v>
       </c>
       <c r="R72" t="n">
-        <v>6607547</v>
+        <v>6607505</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9493,12 +8492,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9509,36 +8508,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>103894692</v>
+        <v>96219599</v>
       </c>
       <c r="B73" t="n">
-        <v>83136</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9546,21 +8535,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3518</v>
+        <v>222412</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -9570,24 +8559,22 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>507989.7213163687</v>
+        <v>507777</v>
       </c>
       <c r="R73" t="n">
-        <v>6607536.206189661</v>
+        <v>6607507</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9611,22 +8598,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9635,39 +8612,28 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>103894694</v>
+        <v>96219600</v>
       </c>
       <c r="B74" t="n">
-        <v>83136</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9675,21 +8641,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3518</v>
+        <v>222412</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -9699,24 +8665,22 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>507960.377339335</v>
+        <v>508111</v>
       </c>
       <c r="R74" t="n">
-        <v>6607506.787855229</v>
+        <v>6607585</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9740,22 +8704,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9764,39 +8718,28 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>103894693</v>
+        <v>96219601</v>
       </c>
       <c r="B75" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9804,48 +8747,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4366</v>
+        <v>222412</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507933.9603704637</v>
+        <v>507683</v>
       </c>
       <c r="R75" t="n">
-        <v>6607531.53255562</v>
+        <v>6607557</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9869,22 +8801,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9893,24 +8815,18 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9920,12 +8836,7 @@
         <v>116215056</v>
       </c>
       <c r="B76" t="n">
-        <v>99994</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10033,54 +8944,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127275094</v>
+        <v>96219581</v>
       </c>
       <c r="B77" t="n">
-        <v>92658</v>
+        <v>101228</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4368</v>
+        <v>222771</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Yttre Munkhyttan, Vstm</t>
+          <t>Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507905</v>
+        <v>507786</v>
       </c>
       <c r="R77" t="n">
-        <v>6607482</v>
+        <v>6607515</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10107,12 +9018,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10121,77 +9032,73 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127275093</v>
+        <v>96219582</v>
       </c>
       <c r="B78" t="n">
-        <v>92658</v>
+        <v>101228</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4368</v>
+        <v>222771</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Yttre Munkhyttan, Vstm</t>
+          <t>Munkhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507893</v>
+        <v>507695</v>
       </c>
       <c r="R78" t="n">
-        <v>6607558</v>
+        <v>6607561</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10218,12 +9125,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10232,26 +9139,664 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>96219583</v>
+      </c>
+      <c r="B79" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>507814</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6607611</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>96219584</v>
+      </c>
+      <c r="B80" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>507684</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6607552</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>96219585</v>
+      </c>
+      <c r="B81" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>508052</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6607380</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>96219587</v>
+      </c>
+      <c r="B82" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>508029</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6607371</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>96219588</v>
+      </c>
+      <c r="B83" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>508014</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6607402</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>96219589</v>
+      </c>
+      <c r="B84" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>508076</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6607450</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
